--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0020.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0020.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Thuộc Tính Resonance của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Thuộc Tính Resonance của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{0} Bạn có thể gọi Phaom để di chuyển.</t>
+          <t>{0} Giờ cậu có thể gọi Phaom để di chuyển rồi.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Nhấn để gọi Phaom cưỡi.</t>
+          <t>Nhấn để gọi Phaom chở đi.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Đã kích hoạt Chỉnh Sửa Data. Bạn có thể điều chỉnh Mainstat của Echo.</t>
+          <t>Điều Chỉnh Dữ Liệu đã kích hoạt. Giờ cậu có thể thay đổi Chỉ Số Chính của Echo.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Đã kích hoạt Chỉnh Sửa Data. Bạn có thể điều chỉnh Mainstat của Echo.</t>
+          <t>Điều Chỉnh Dữ Liệu đã kích hoạt. Giờ cậu có thể thay đổi Chỉ Số Chính của Echo.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Đã kích hoạt Chỉnh Sửa Data. Bạn có thể điều chỉnh Mainstat của Echo.</t>
+          <t>Điều Chỉnh Dữ Liệu đã kích hoạt. Giờ cậu có thể thay đổi Chỉ Số Chính của Echo.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Ưu đãi Birthday Độc Quyền đã kích hoạt. Bạn có thể vào Hồ Sơ để thay đổi ngày sinh ngay bây giờ.</t>
+          <t>Lời Chúc Mừng Sinh Nhật Đặc Biệt đã kích hoạt. Bạn có thể vào Hồ Sơ để thay đổi ngày sinh của mình.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ưu đãi Birthday Độc Quyền đã kích hoạt. Bạn có thể vào Hồ Sơ để thay đổi ngày sinh ngay bây giờ.</t>
+          <t>Lời Chúc Mừng Sinh Nhật Đặc Biệt đã kích hoạt. Bạn có thể vào Hồ Sơ để thay đổi ngày sinh của mình.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Ưu đãi Birthday Độc Quyền đã kích hoạt. Bạn có thể vào Hồ Sơ để thay đổi ngày sinh ngay bây giờ.</t>
+          <t>Lời Chúc Mừng Sinh Nhật Đặc Biệt đã kích hoạt. Bạn có thể vào Hồ Sơ để thay đổi ngày sinh của mình.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Chọn ngày sinh của bạn để mở khóa một phước lành độc quyền vào ngày sinh nhật.</t>
+          <t>Chọn ngày sinh để nhận phước lành độc quyền vào ngày sinh nhật của bạn.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Chọn ngày sinh của bạn để mở khóa một phước lành độc quyền vào ngày sinh nhật.</t>
+          <t>Chọn ngày sinh để nhận phước lành độc quyền vào ngày sinh nhật của bạn.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Chọn ngày sinh của bạn để mở khóa một phước lành độc quyền vào ngày sinh nhật.</t>
+          <t>Chọn ngày sinh để nhận phước lành độc quyền vào ngày sinh nhật của bạn.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Chọn ngày sinh của bạn để mở khóa một phước lành độc quyền vào ngày sinh nhật.</t>
+          <t>Chọn ngày sinh để nhận phước lành độc quyền vào ngày sinh nhật của bạn.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Chọn ngày sinh của bạn để mở khóa một phước lành độc quyền vào ngày sinh nhật.</t>
+          <t>Chọn ngày sinh để nhận phước lành độc quyền vào ngày sinh nhật của bạn.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Chọn ngày sinh của bạn để mở khóa một phước lành độc quyền vào ngày sinh nhật.</t>
+          <t>Chọn ngày sinh để nhận phước lành độc quyền vào ngày sinh nhật của bạn.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Xem quy tắc Sinh Nhật tại đây.</t>
+          <t>Xem quy định về Sinh Nhật tại đây.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Xem quy tắc Sinh Nhật tại đây.</t>
+          <t>Xem quy định về Sinh Nhật tại đây.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Xem quy tắc Sinh Nhật tại đây.</t>
+          <t>Xem quy định về Sinh Nhật tại đây.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Huấn Luyện để nhận Xúc Xắc Ma Thuật giúp di chuyển Khối Lập Phương của bạn.</t>
+          <t>Hoàn thành Nhiệm Vụ Huấn Luyện để nhận Xúc Xắc Ma Pháp giúp di chuyển các Khối Lập Phương của cậu.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{0} Hoàn thành Training Tasks để nhận Magic Dice di chuyển Cubes của bạn về phía trước.</t>
+          <t>Hoàn thành Nhiệm Vụ Huấn Luyện để nhận Magic Dice giúp di chuyển các Cube của cậu tiến lên.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Huấn Luyện để nhận Xúc Xắc Ma Thuật giúp di chuyển Khối Lập Phương của bạn.</t>
+          <t>Hoàn thành Nhiệm Vụ Huấn Luyện để nhận Xúc Xắc Ma Pháp giúp di chuyển các Khối Lập Phương của cậu.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Lắc xúc xắc để di chuyển Cube và thu thập phần thưởng trên các ô bạn đi qua.</t>
+          <t>Gieo xúc xắc để di chuyển Khối Lập Phương và thu thập phần thưởng trên các ô cậu đi qua.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{0} Roll xúc xắc để di chuyển Cube và thu thập phần thưởng trên các ô đi qua.</t>
+          <t>{0} Lắc xúc xắc để di chuyển Khối Lập Phương và thu thập phần thưởng trên các ô đi qua.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Lắc xúc xắc để di chuyển Cube và thu thập phần thưởng trên các ô bạn đi qua.</t>
+          <t>Gieo xúc xắc để di chuyển Khối Lập Phương và thu thập phần thưởng trên các ô cậu đi qua.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kết thúc lượt để nhận thưởng vòng này.</t>
+          <t>Kết thúc lượt của cậu để nhận thưởng vòng này.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Kết thúc lượt để nhận thưởng vòng này.</t>
+          <t>Kết thúc lượt của cậu để nhận thưởng vòng này.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Kết thúc lượt để nhận thưởng vòng này.</t>
+          <t>Kết thúc lượt của cậu để nhận thưởng vòng này.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Xem Báo Cáo Round Đấu tại đây</t>
+          <t>Xem Báo Cáo Vòng tại đây</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{0} Check Báo Cáo Round tại đây</t>
+          <t>Xem Báo Cáo Vòng Đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Xem Báo Cáo Round Đấu tại đây</t>
+          <t>Xem Báo Cáo Vòng tại đây</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Enter Thế giới Cube để tương tác với các Cube và xem chúng làm gì nhé!</t>
+          <t>Bước vào Thế giới Cube để tương tác với các Cube và xem chúng làm gì!</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Enter Thế giới Cube để tương tác với các Cube và xem chúng làm gì nhé!</t>
+          <t>Bước vào Thế giới Cube để tương tác với các Cube và xem chúng làm gì!</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Enter Thế giới Cube để tương tác với các Cube và xem chúng làm gì nhé!</t>
+          <t>Bước vào Thế giới Cube để tương tác với các Cube và xem chúng làm gì!</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để vào Abbowser Castle</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Lâu Đài Abbowser.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để vào Abbowser Castle</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Lâu Đài Abbowser.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để vào Abbowser Castle</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Lâu Đài Abbowser.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Tiến vào Abbowser Castle và đối đầu với Abbowser cùng tay chân của hắn!</t>
+          <t>Tiến vào Lâu Đài Abbowser và đối đầu với hắn cùng bè lũ tay sai!</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Tiến vào Abbowser Castle và đối đầu với Abbowser cùng tay chân của hắn!</t>
+          <t>Tiến vào Lâu Đài Abbowser và đối đầu với hắn cùng bè lũ tay sai!</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Tiến vào Abbowser Castle và đối đầu với Abbowser cùng tay chân của hắn!</t>
+          <t>Tiến vào Lâu Đài Abbowser và đối đầu với hắn cùng bè lũ tay sai!</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Chọn Hỗ Trợ Cube cho Resonator của bạn.</t>
+          <t>Chọn một Khối Hỗ Trợ cho Resonator của bạn.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{0} Hãy chọn một Hỗ Trợ Cube cho Resonator của bạn.</t>
+          <t>Chọn một Support Cube cho Resonator của cậu.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Chọn Hỗ Trợ Cube cho Resonator của bạn.</t>
+          <t>Chọn một Khối Hỗ Trợ cho Resonator của bạn.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Chọn Hỗ Trợ Cube.</t>
+          <t>Chọn Khối Hỗ Trợ</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Chọn Hỗ Trợ Cube.</t>
+          <t>Chọn Khối Hỗ Trợ</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Chọn Hỗ Trợ Cube.</t>
+          <t>Chọn Khối Hỗ Trợ</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Xem hiệu ứng của Hỗ Trợ Cube tại đây.</t>
+          <t>Xem hiệu ứng của Khối Hỗ Trợ tại đây.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Xem hiệu ứng của Hỗ Trợ Cube tại đây.</t>
+          <t>Xem hiệu ứng của Khối Hỗ Trợ tại đây.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Xem hiệu ứng của Hỗ Trợ Cube tại đây.</t>
+          <t>Xem hiệu ứng của Khối Hỗ Trợ tại đây.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để trang bị Hỗ Trợ Cube.</t>
+          <t>Nhấn vào đây để trang bị Khối Lập Phương Hỗ Trợ của bạn.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để trang bị Hỗ Trợ Cube.</t>
+          <t>Nhấn vào đây để trang bị Khối Lập Phương Hỗ Trợ của bạn.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để trang bị Hỗ Trợ Cube.</t>
+          <t>Nhấn vào đây để trang bị Khối Lập Phương Hỗ Trợ của bạn.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Kiểm tra tiến độ nhận thưởng tại đây. Bạn có thể {Cus:Ipt,Touch=tap PC=bấm Gamepad=press} để xem chi tiết nhiệm vụ.</t>
+          <t>Kiểm tra tiến độ nhận thưởng tại đây. Bạn có thể {Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem chi tiết nhiệm vụ.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Kiểm tra tiến độ nhận thưởng tại đây. Bạn có thể {Cus:Ipt,Touch=tap PC=bấm Gamepad=press} để xem chi tiết nhiệm vụ.</t>
+          <t>Kiểm tra tiến độ nhận thưởng tại đây. Bạn có thể {Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem chi tiết nhiệm vụ.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Kiểm tra tiến độ nhận thưởng tại đây. Bạn có thể {Cus:Ipt,Touch=tap PC=bấm Gamepad=press} để xem chi tiết nhiệm vụ.</t>
+          <t>Kiểm tra tiến độ nhận thưởng tại đây. Bạn có thể {Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem chi tiết nhiệm vụ.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Bạn nhận được một đống đồ ăn vặt! Đến lúc tăng sức mạnh cho Cubes rồi!</t>
+          <t>Cậu có cả đống đồ ăn vặt! Đến lúc nạp năng lượng cho Khối Lập Phương rồi!</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{0} Bạn nhận được một đống đồ ăn vặt! Đến lúc tiếp năng lượng cho Cubes rồi!</t>
+          <t>{0} Cậu nhận được một đống đồ ăn vặt! Đến lúc nạp năng lượng cho Cubes thôi!</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Bạn nhận được một đống đồ ăn vặt! Đến lúc tăng sức mạnh cho Cubes rồi!</t>
+          <t>Cậu có cả đống đồ ăn vặt! Đến lúc nạp năng lượng cho Khối Lập Phương rồi!</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Equip Mô-đun Data cho Cube để tăng chỉ số và Kỹ Năng.</t>
+          <t>Gắn Mô-đun Dữ Liệu lên Khối Lập Phương để tăng chỉ số và khả năng của chúng.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{0} Equip Mô-đun Dữ liệu cho Cube để tăng chỉ số và Kỹ năng của chúng.</t>
+          <t>{0} Trang bị Mô-đun Dữ Liệu cho Khối Lập Phương để tăng chỉ số và Kỹ Năng.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Equip Mô-đun Data cho Cube để tăng chỉ số và Kỹ Năng.</t>
+          <t>Gắn Mô-đun Dữ Liệu lên Khối Lập Phương để tăng chỉ số và khả năng của chúng.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Chọn Mô-đun Dữ liệu để trang bị cho Khối Lập phương của bạn.</t>
+          <t>Chọn Mô-đun Dữ liệu để trang bị cho Khối Lập phương của cậu.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Chọn Mô-đun Dữ liệu để trang bị cho Khối Lập phương của bạn.</t>
+          <t>Chọn Mô-đun Dữ liệu để trang bị cho Khối Lập phương của cậu.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Chọn Mô-đun Dữ liệu để trang bị cho Khối Lập phương của bạn.</t>
+          <t>Chọn Mô-đun Dữ liệu để trang bị cho Khối Lập phương của cậu.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Bạn tìm thấy đồ ăn vặt Cube trong Lâu Đài Abbowser! {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để tăng cấp.</t>
+          <t>Bạn tìm thấy bánh Cube trong Lâu Đài Abbowser! {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Bạn tìm thấy đồ ăn vặt Cube trong Lâu Đài Abbowser! {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để tăng cấp.</t>
+          <t>Bạn tìm thấy bánh Cube trong Lâu Đài Abbowser! {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Bạn tìm thấy đồ ăn vặt Cube trong Lâu Đài Abbowser! {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để tăng cấp.</t>
+          <t>Bạn tìm thấy bánh Cube trong Lâu Đài Abbowser! {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Đã mở khóa khe Cube Ability Mô-đun. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} để trang bị vào khe.</t>
+          <t>Khe Mô-đun Năng Lực Khối Lập Phương đã mở khóa. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để trang bị vào khe.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Đã mở khóa khe Cube Ability Mô-đun. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} để trang bị vào khe.</t>
+          <t>Khe Mô-đun Năng Lực Khối Lập Phương đã mở khóa. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để trang bị vào khe.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Đã mở khóa khe Cube Ability Mô-đun. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} để trang bị vào khe.</t>
+          <t>Khe Mô-đun Năng Lực Khối Lập Phương đã mở khóa. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để trang bị vào khe.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để trang bị Mô-đun Thức tỉnh độc quyền của Khối này.</t>
+          <t>Nhấn vào đây để trang bị Mô-đun Thức Tỉnh độc quyền của Khối Lập Phương này.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để trang bị Mô-đun Thức tỉnh độc quyền của Khối này.</t>
+          <t>Nhấn vào đây để trang bị Mô-đun Thức Tỉnh độc quyền của Khối Lập Phương này.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để trang bị Mô-đun Thức tỉnh độc quyền của Khối này.</t>
+          <t>Nhấn vào đây để trang bị Mô-đun Thức Tỉnh độc quyền của Khối Lập Phương này.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Bạn có thể Decompile các Data Mô-đun dư thừa thành vật liệu nâng cấp cho Cube của mình.</t>
+          <t>Cậu có thể Giải Cấu trúc các Mô-đun Dữ liệu dư thừa thành vật liệu nâng cấp cho Khối Lập Phương của mình.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Bạn có thể Decompile các Data Mô-đun dư thừa thành vật liệu nâng cấp cho Cube của mình.</t>
+          <t>Cậu có thể Giải Cấu trúc các Mô-đun Dữ liệu dư thừa thành vật liệu nâng cấp cho Khối Lập Phương của mình.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Bạn có thể Decompile các Data Mô-đun dư thừa thành vật liệu nâng cấp cho Cube của mình.</t>
+          <t>Cậu có thể Giải Cấu trúc các Mô-đun Dữ liệu dư thừa thành vật liệu nâng cấp cho Khối Lập Phương của mình.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Có thể mua Data Modules tại Abbowser's Shop.</t>
+          <t>Có thể mua Mô-đun Dữ Liệu tại Cửa Hàng của Abbowser.</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Có thể mua Data Modules tại Abbowser's Shop.</t>
+          <t>Có thể mua Mô-đun Dữ Liệu tại Cửa Hàng của Abbowser.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Có thể mua Data Modules tại Abbowser's Shop.</t>
+          <t>Có thể mua Mô-đun Dữ Liệu tại Cửa Hàng của Abbowser.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ thời hạn trong sự kiện để nhận phần thưởng đặc biệt.</t>
+          <t>Hoàn thành các nhiệm vụ giới hạn thời gian trong sự kiện để nhận phần thưởng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ thời hạn trong sự kiện để nhận phần thưởng đặc biệt.</t>
+          <t>Hoàn thành các nhiệm vụ giới hạn thời gian trong sự kiện để nhận phần thưởng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ thời hạn trong sự kiện để nhận phần thưởng đặc biệt.</t>
+          <t>Hoàn thành các nhiệm vụ giới hạn thời gian trong sự kiện để nhận phần thưởng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Tại đây bạn có thể bật/tắt trò chuyện trực tiếp, chọn biểu cảm và gửi tin nhắn!</t>
+          <t>Tại đây, cậu có thể bật/tắt trò chuyện trực tiếp, chọn biểu cảm và gửi tin nhắn!</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Tại đây bạn có thể bật/tắt trò chuyện trực tiếp, chọn biểu cảm và gửi tin nhắn!</t>
+          <t>Tại đây, cậu có thể bật/tắt trò chuyện trực tiếp, chọn biểu cảm và gửi tin nhắn!</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Tại đây bạn có thể bật/tắt trò chuyện trực tiếp, chọn biểu cảm và gửi tin nhắn!</t>
+          <t>Tại đây, cậu có thể bật/tắt trò chuyện trực tiếp, chọn biểu cảm và gửi tin nhắn!</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Đây là Cube đang chuẩn bị cho trận đấu tiếp theo.</t>
+          <t>Đây là khối Lập Phương đang chuẩn bị cho trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Đây là Cube đang chuẩn bị cho trận đấu tiếp theo.</t>
+          <t>Đây là khối Lập Phương đang chuẩn bị cho trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Đây là Cube đang chuẩn bị cho trận đấu tiếp theo.</t>
+          <t>Đây là khối Lập Phương đang chuẩn bị cho trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Hiển thị thời gian bắt đầu của trận đấu tiếp theo.</t>
+          <t>Màn hình này hiển thị thời gian bắt đầu trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Hiển thị thời gian bắt đầu của trận đấu tiếp theo.</t>
+          <t>Màn hình này hiển thị thời gian bắt đầu trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Hiển thị thời gian bắt đầu của trận đấu tiếp theo.</t>
+          <t>Màn hình này hiển thị thời gian bắt đầu trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ Race và xem lại replay.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Race để kiểm tra tiến độ cuộc đua và xem lại các màn replay.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ Race và xem lại replay.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Race để kiểm tra tiến độ cuộc đua và xem lại các màn replay.</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ Race và xem lại replay.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Race để kiểm tra tiến độ cuộc đua và xem lại các màn replay.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Hiển thị Tiến Độ Cuộc Race và các Khối Lập Phương còn tranh tài.</t>
+          <t>Màn hình này hiển thị Tiến Độ Cuộc Đua và số Khối Lập Phương vẫn còn tranh đấu.</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Hiển thị Tiến Độ Cuộc Race và các Khối Lập Phương còn tranh tài.</t>
+          <t>Màn hình này hiển thị Tiến Độ Cuộc Đua và số Khối Lập Phương vẫn còn tranh đấu.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Hiển thị Tiến Độ Cuộc Race và các Khối Lập Phương còn tranh tài.</t>
+          <t>Màn hình này hiển thị Tiến Độ Cuộc Đua và số Khối Lập Phương vẫn còn tranh đấu.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ hằng ngày để nhận Hỗ trợ Popularity</t>
+          <t>Hoàn thành Nhiệm Vụ Hằng Ngày để nhận Hỗ Trợ Uy Tín</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>{0} Hoàn thành Daily Tasks để nhận Hỗ Trợ Uy Tín.</t>
+          <t>Hoàn thành Nhiệm Vụ Hằng Ngày để nhận Hỗ Trợ Độ Phổ Biến.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ hằng ngày để nhận Hỗ trợ Popularity</t>
+          <t>Hoàn thành Nhiệm Vụ Hằng Ngày để nhận Hỗ Trợ Uy Tín</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Chọn một Cube để Hỗ Trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó thắng.</t>
+          <t>Chọn một Khối Lập Phương để hỗ trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó chiến thắng</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>{0} Chọn một Khối lập phương để hỗ trợ và nhận lượng Popularity khổng lồ nếu nó chiến thắng.</t>
+          <t>Chọn một Khối Lập Phương để Hỗ Trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Chọn một Cube để Hỗ Trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó thắng.</t>
+          <t>Chọn một Khối Lập Phương để hỗ trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó chiến thắng</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Khối Cube có Tỷ Lệ Thua Cao hơn sẽ mang lại nhiều phần thưởng Popularity hơn nếu chiến thắng.</t>
+          <t>Khối Lập Phương có Tỷ Lệ Thua Lợi Nhuận cao hơn sẽ mang lại phần thưởng Danh Vọng nhiều hơn nếu chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Khối Cube có Tỷ Lệ Thua Cao hơn sẽ mang lại nhiều phần thưởng Popularity hơn nếu chiến thắng.</t>
+          <t>Khối Lập Phương có Tỷ Lệ Thua Lợi Nhuận cao hơn sẽ mang lại phần thưởng Danh Vọng nhiều hơn nếu chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Khối Cube có Tỷ Lệ Thua Cao hơn sẽ mang lại nhiều phần thưởng Popularity hơn nếu chiến thắng.</t>
+          <t>Khối Lập Phương có Tỷ Lệ Thua Lợi Nhuận cao hơn sẽ mang lại phần thưởng Danh Vọng nhiều hơn nếu chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Tiêu hao lượng Popularity khác nhau để hỗ trợ Cube hiện tại của bạn</t>
+          <t>Tiêu thụ Lượng Yêu Thích để hỗ trợ Khối Lập Phương hiện tại.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Tiêu hao lượng Popularity khác nhau để hỗ trợ Cube hiện tại của bạn</t>
+          <t>Tiêu thụ Lượng Yêu Thích để hỗ trợ Khối Lập Phương hiện tại.</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Tiêu hao lượng Popularity khác nhau để hỗ trợ Cube hiện tại của bạn</t>
+          <t>Tiêu thụ Lượng Yêu Thích để hỗ trợ Khối Lập Phương hiện tại.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng Danh Vọng nếu Cube bạn ủng hộ giành vị trí đầu tiên!</t>
+          <t>Nhận phần thưởng Độ Nổi Tiếng nếu Khối Lập Phương bạn ủng hộ về nhất!</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng Danh Vọng nếu Cube bạn ủng hộ giành vị trí đầu tiên!</t>
+          <t>Nhận phần thưởng Độ Nổi Tiếng nếu Khối Lập Phương bạn ủng hộ về nhất!</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng Danh Vọng nếu Cube bạn ủng hộ giành vị trí đầu tiên!</t>
+          <t>Nhận phần thưởng Độ Nổi Tiếng nếu Khối Lập Phương bạn ủng hộ về nhất!</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Kiểm tra dữ liệu và xem lại trận đấu tại đây.</t>
+          <t>Xem lại dữ liệu và phát lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Kiểm tra dữ liệu và xem lại trận đấu tại đây.</t>
+          <t>Xem lại dữ liệu và phát lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Kiểm tra dữ liệu và xem lại trận đấu tại đây.</t>
+          <t>Xem lại dữ liệu và phát lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Dữ liệu và bản ghi lại các trận đấu trước có thể được tìm thấy tại đây.</t>
+          <t>Dữ liệu và bản ghi lại các trận đấu trước có thể tìm thấy tại đây.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Dữ liệu và bản ghi lại các trận đấu trước có thể được tìm thấy tại đây.</t>
+          <t>Dữ liệu và bản ghi lại các trận đấu trước có thể tìm thấy tại đây.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Dữ liệu và bản ghi lại các trận đấu trước có thể được tìm thấy tại đây.</t>
+          <t>Dữ liệu và bản ghi lại các trận đấu trước có thể tìm thấy tại đây.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Event để nhận phần thưởng giới hạn thời gian.</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Event để nhận phần thưởng giới hạn thời gian.</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Event để nhận phần thưởng giới hạn thời gian.</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Hãy bắt đầu tưởng tượng câu chuyện được kể qua những giai điệu!</t>
+          <t>Hãy bắt đầu tưởng tượng câu chuyện sẽ diễn biến ra sao qua những giai điệu!</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Hãy bắt đầu tưởng tượng câu chuyện được kể qua những giai điệu!</t>
+          <t>Hãy bắt đầu tưởng tượng câu chuyện sẽ diễn biến ra sao qua những giai điệu!</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Hãy bắt đầu tưởng tượng câu chuyện được kể qua những giai điệu!</t>
+          <t>Hãy bắt đầu tưởng tượng câu chuyện sẽ diễn biến ra sao qua những giai điệu!</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Chọn tùy chọn này và khám phá diễn biến câu chuyện.</t>
+          <t>Chọn lựa chọn này và xem câu chuyện sẽ diễn biến ra sao.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Chọn tùy chọn này và khám phá diễn biến câu chuyện.</t>
+          <t>Chọn lựa chọn này và xem câu chuyện sẽ diễn biến ra sao.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Chọn tùy chọn này và khám phá diễn biến câu chuyện.</t>
+          <t>Chọn lựa chọn này và xem câu chuyện sẽ diễn biến ra sao.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Kết thúc thực sự vẫn còn thiếu vài mảnh ghép. Hãy thử lại nào!</t>
+          <t>Kết thúc thực sự vẫn còn thiếu vài mảnh ghép. Thử lại nào!</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Kết thúc thực sự vẫn còn thiếu vài mảnh ghép. Hãy thử lại nào!</t>
+          <t>Kết thúc thực sự vẫn còn thiếu vài mảnh ghép. Thử lại nào!</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Kết thúc thực sự vẫn còn thiếu vài mảnh ghép. Hãy thử lại nào!</t>
+          <t>Kết thúc thực sự vẫn còn thiếu vài mảnh ghép. Thử lại nào!</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Hãy thử lại để tìm ra cái kết thực sự của câu chuyện!</t>
+          <t>Thử lại lần nữa để tìm ra cái kết thật sự của câu chuyện nào!</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Hãy thử lại để tìm ra cái kết thực sự của câu chuyện!</t>
+          <t>Thử lại lần nữa để tìm ra cái kết thật sự của câu chuyện nào!</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Hãy thử lại để tìm ra cái kết thực sự của câu chuyện!</t>
+          <t>Thử lại lần nữa để tìm ra cái kết thật sự của câu chuyện nào!</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Tiêu hao Inspiration để mở khóa thêm kết thúc cho câu chuyện.</t>
+          <t>Tiêu hao Cảm Hứng để mở khóa thêm kết thúc cho câu chuyện.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Tiêu hao Inspiration để mở khóa thêm kết thúc cho câu chuyện.</t>
+          <t>Tiêu hao Cảm Hứng để mở khóa thêm kết thúc cho câu chuyện.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tiêu hao Inspiration để mở khóa thêm kết thúc cho câu chuyện.</t>
+          <t>Tiêu hao Cảm Hứng để mở khóa thêm kết thúc cho câu chuyện.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Điểm Inspiration được phục hồi 1 điểm mỗi ngày. Dùng để mở khóa các lựa chọn đặc biệt.</t>
+          <t>Mỗi ngày phục hồi 1 điểm Cảm Hứng. Dùng để mở khóa các lựa chọn đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Điểm Inspiration được phục hồi 1 điểm mỗi ngày. Dùng để mở khóa các lựa chọn đặc biệt.</t>
+          <t>Mỗi ngày phục hồi 1 điểm Cảm Hứng. Dùng để mở khóa các lựa chọn đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Điểm Inspiration được phục hồi 1 điểm mỗi ngày. Dùng để mở khóa các lựa chọn đặc biệt.</t>
+          <t>Mỗi ngày phục hồi 1 điểm Cảm Hứng. Dùng để mở khóa các lựa chọn đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Tái hiện câu chuyện và khám phá những kết thúc phân nhánh tại đây!</t>
+          <t>Sống lại câu chuyện và khám phá những kết thúc khác nhau tại đây!</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Tái hiện câu chuyện và khám phá những kết thúc phân nhánh tại đây!</t>
+          <t>Sống lại câu chuyện và khám phá những kết thúc khác nhau tại đây!</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Tái hiện câu chuyện và khám phá những kết thúc phân nhánh tại đây!</t>
+          <t>Sống lại câu chuyện và khám phá những kết thúc khác nhau tại đây!</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Mỗi chương có nhiều kết thúc. Hoàn thành tất cả để nhận phần thưởng bổ sung!</t>
+          <t>Mỗi chương đều có nhiều kết thúc khác nhau. Hoàn thành tất cả để nhận thêm phần thưởng!</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Mỗi chương có nhiều kết thúc. Hoàn thành tất cả để nhận phần thưởng bổ sung!</t>
+          <t>Mỗi chương đều có nhiều kết thúc khác nhau. Hoàn thành tất cả để nhận thêm phần thưởng!</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Mỗi chương có nhiều kết thúc. Hoàn thành tất cả để nhận phần thưởng bổ sung!</t>
+          <t>Mỗi chương đều có nhiều kết thúc khác nhau. Hoàn thành tất cả để nhận thêm phần thưởng!</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} "Watch Films" để biết Rạp nào hiện có thể thử thách.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} "Xem Phim" để biết Nhà hát nào hiện có thể khiêu chiến.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=press Gamepad=press} "Watch Films" để xem rạp nào hiện có thể thách đấu.</t>
+          <t>Nhấn {0} "Xem Phim" để biết Nhà Hát nào có thể thách đấu</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} "Watch Films" để biết Rạp nào hiện có thể thử thách.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} "Xem Phim" để biết Nhà hát nào hiện có thể khiêu chiến.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem Film</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Phim.</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem Film</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Phim.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem Film</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Phim.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Lý Thuyết Film mở khóa một số khả năng đặc biệt trong mỗi bộ Film.</t>
+          <t>Lý Thuyết Phim mở khóa một số khả năng đặc biệt trong từng bộ phim.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Lý Thuyết Film mở khóa một số khả năng đặc biệt trong mỗi bộ Film.</t>
+          <t>Lý Thuyết Phim mở khóa một số khả năng đặc biệt trong từng bộ phim.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Lý Thuyết Film mở khóa một số khả năng đặc biệt trong mỗi bộ Film.</t>
+          <t>Lý Thuyết Phim mở khóa một số khả năng đặc biệt trong từng bộ phim.</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Thách đấu Screenplay để mở khóa vật phẩm Film Theory.</t>
+          <t>Hoàn thành Kịch Bản để mở khóa vật phẩm Lý Thuyết Điện Ảnh.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Thách đấu Screenplay để mở khóa vật phẩm Film Theory.</t>
+          <t>Hoàn thành Kịch Bản để mở khóa vật phẩm Lý Thuyết Điện Ảnh.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Thách đấu Screenplay để mở khóa vật phẩm Film Theory.</t>
+          <t>Hoàn thành Kịch Bản để mở khóa vật phẩm Lý Thuyết Điện Ảnh.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Lựa chọn và nhánh câu chuyện của bạn dẫn đến những kết thúc khác nhau trong Screenplay.</t>
+          <t>Những lựa chọn và nhánh câu chuyện của cậu sẽ dẫn đến những kết thúc khác nhau trong Kịch Bản.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Lựa chọn và nhánh câu chuyện của bạn dẫn đến những kết thúc khác nhau trong Screenplay.</t>
+          <t>Những lựa chọn và nhánh câu chuyện của cậu sẽ dẫn đến những kết thúc khác nhau trong Kịch Bản.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Lựa chọn và nhánh câu chuyện của bạn dẫn đến những kết thúc khác nhau trong Screenplay.</t>
+          <t>Những lựa chọn và nhánh câu chuyện của cậu sẽ dẫn đến những kết thúc khác nhau trong Kịch Bản.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Hoàn thành các Challenge Goal giới hạn thời gian để nhận phần thưởng thêm.</t>
+          <t>Hoàn thành các Mục Tiêu Thử Thách giới hạn thời gian để nhận thêm phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Hoàn thành các Challenge Goal giới hạn thời gian để nhận phần thưởng thêm.</t>
+          <t>Hoàn thành các Mục Tiêu Thử Thách giới hạn thời gian để nhận thêm phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Hoàn thành các Challenge Goal giới hạn thời gian để nhận phần thưởng thêm.</t>
+          <t>Hoàn thành các Mục Tiêu Thử Thách giới hạn thời gian để nhận thêm phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem các Trial Resonators hiện có.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các Resonator Thử Nghiệm hiện có.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem các Trial Resonators hiện có.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các Resonator Thử Nghiệm hiện có.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem các Trial Resonators hiện có.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các Resonator Thử Nghiệm hiện có.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Xem các kết thúc đã mở khóa và nhận phần thưởng độc quyền!</t>
+          <t>Xem các kết thúc đã mở khóa và nhận phần thưởng độc quyền nào!</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Xem các kết thúc đã mở khóa và nhận phần thưởng độc quyền!</t>
+          <t>Xem các kết thúc đã mở khóa và nhận phần thưởng độc quyền nào!</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Xem các kết thúc đã mở khóa và nhận phần thưởng độc quyền!</t>
+          <t>Xem các kết thúc đã mở khóa và nhận phần thưởng độc quyền nào!</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Xem lại diễn biến sự kiện trong quá trình khám phá và nhận thưởng!</t>
+          <t>Xem lại diễn biến trong quá trình thám hiểm và nhận thưởng!</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Xem lại diễn biến sự kiện trong quá trình khám phá và nhận thưởng!</t>
+          <t>Xem lại diễn biến trong quá trình thám hiểm và nhận thưởng!</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Xem lại diễn biến sự kiện trong quá trình khám phá và nhận thưởng!</t>
+          <t>Xem lại diễn biến trong quá trình thám hiểm và nhận thưởng!</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Explore Screenplay để kiếm Token, sau đó đổi lấy phần thưởng tại Cửa Hàng Cầm Đồ Giấc Mơ.</t>
+          <t>Khám phá Kịch Bản để kiếm Token, đổi lấy phần thưởng tại Tiệm Cầm Đồ Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Explore Screenplay để kiếm Token, sau đó đổi lấy phần thưởng tại Cửa Hàng Cầm Đồ Giấc Mơ.</t>
+          <t>Khám phá Kịch Bản để kiếm Token, đổi lấy phần thưởng tại Tiệm Cầm Đồ Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Explore Screenplay để kiếm Token, sau đó đổi lấy phần thưởng tại Cửa Hàng Cầm Đồ Giấc Mơ.</t>
+          <t>Khám phá Kịch Bản để kiếm Token, đổi lấy phần thưởng tại Tiệm Cầm Đồ Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Có thể hoàn thành Challenges cùng người chơi khác trong chế độ Co-op.</t>
+          <t>Có thể hoàn thành Thử Thách cùng người chơi khác trong chế độ Đồng Đội.</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Có thể hoàn thành Challenges cùng người chơi khác trong chế độ Co-op.</t>
+          <t>Có thể hoàn thành Thử Thách cùng người chơi khác trong chế độ Đồng Đội.</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Có thể hoàn thành Challenges cùng người chơi khác trong chế độ Co-op.</t>
+          <t>Có thể hoàn thành Thử Thách cùng người chơi khác trong chế độ Đồng Đội.</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
+          <t>Màn hình này hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
+          <t>Màn hình này hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
+          <t>Màn hình này hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Thời gian bắt đầu của hai trận đấu tiếp theo được hiển thị tại đây.</t>
+          <t>Thời gian bắt đầu hai trận đấu tiếp theo được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Thời gian bắt đầu của hai trận đấu tiếp theo được hiển thị tại đây.</t>
+          <t>Thời gian bắt đầu hai trận đấu tiếp theo được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Thời gian bắt đầu của hai trận đấu tiếp theo được hiển thị tại đây.</t>
+          <t>Thời gian bắt đầu hai trận đấu tiếp theo được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ Race và xem lại replay.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Race để kiểm tra tiến độ cuộc đua và xem lại các màn replay.</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ cuộc đua và xem lại các đoạn phát lại.</t>
+          <t>{0} {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} nút "Đua" để kiểm tra tiến độ và xem lại các màn đua.</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ Race và xem lại replay.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Race để kiểm tra tiến độ cuộc đua và xem lại các màn replay.</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Bạn đã nhận được Awakening Mô-đun. Hãy trang bị nó lên Cube của bạn!</t>
+          <t>Bạn đã nhận được một Mô-đun Thức Tỉnh. Hãy trang bị nó lên Khối Lập Phương của bạn!</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Bạn đã nhận được Awakening Mô-đun. Hãy trang bị nó lên Cube của bạn!</t>
+          <t>Bạn đã nhận được một Mô-đun Thức Tỉnh. Hãy trang bị nó lên Khối Lập Phương của bạn!</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Bạn đã nhận được Awakening Mô-đun. Hãy trang bị nó lên Cube của bạn!</t>
+          <t>Bạn đã nhận được một Mô-đun Thức Tỉnh. Hãy trang bị nó lên Khối Lập Phương của bạn!</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Mô-đun Dữ liệu có thể mua tại Cửa hàng Abbowser.</t>
+          <t>Các Mô-đun Dữ liệu có thể mua tại Cửa hàng Abbowser.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Mô-đun Dữ liệu có thể mua tại Cửa hàng Abbowser.</t>
+          <t>Các Mô-đun Dữ liệu có thể mua tại Cửa hàng Abbowser.</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Mô-đun Dữ liệu có thể mua tại Cửa hàng Abbowser.</t>
+          <t>Các Mô-đun Dữ liệu có thể mua tại Cửa hàng Abbowser.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả Thử thách Giới hạn thời gian để nhận Ấn Riêng độc quyền.</t>
+          <t>Hoàn thành tất cả mục tiêu Thử Thách Giới Hạn để nhận Ấn Tượng độc quyền.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả Thử thách Giới hạn thời gian để nhận Ấn Riêng độc quyền.</t>
+          <t>Hoàn thành tất cả mục tiêu Thử Thách Giới Hạn để nhận Ấn Tượng độc quyền.</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả Thử thách Giới hạn thời gian để nhận Ấn Riêng độc quyền.</t>
+          <t>Hoàn thành tất cả mục tiêu Thử Thách Giới Hạn để nhận Ấn Tượng độc quyền.</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Dùng {0} Kỹ Năng Cube để đánh bại tay sai của Abbowser!</t>
+          <t>{0} Dùng Kỹ Năng Khối để đánh bại tay sai của Abbowser!</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Dùng Kỹ Năng Cube để đánh bại tay sai của Abbowser!</t>
+          <t>Dùng Kỹ Năng Cube tiêu diệt tay sai của Abbowser!</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Chỉ số hoạt động được tăng cường nhờ Mô-đun Dữ liệu!</t>
+          <t>Chỉ số của Cộng Hưởng Giả hiện tại được tăng cường nhờ Mô-đun Dữ Liệu!</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Chỉ số hoạt động được tăng cường nhờ Mô-đun Dữ liệu!</t>
+          <t>Chỉ số của Cộng Hưởng Giả hiện tại được tăng cường nhờ Mô-đun Dữ Liệu!</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Chỉ số hoạt động được tăng cường nhờ Mô-đun Dữ liệu!</t>
+          <t>Chỉ số của Cộng Hưởng Giả hiện tại được tăng cường nhờ Mô-đun Dữ Liệu!</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Cách Mô-đun Dữ liệu tăng cường chỉ số chưa kích hoạt.</t>
+          <t>Đây là cách Mô-đun Dữ liệu tăng cường chỉ số không hoạt động ngay lúc này.</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Cách Mô-đun Dữ liệu tăng cường chỉ số chưa kích hoạt.</t>
+          <t>Đây là cách Mô-đun Dữ liệu tăng cường chỉ số không hoạt động ngay lúc này.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Cách Mô-đun Dữ liệu tăng cường chỉ số chưa kích hoạt.</t>
+          <t>Đây là cách Mô-đun Dữ liệu tăng cường chỉ số không hoạt động ngay lúc này.</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Việc gieo xúc xắc sẽ quyết định thứ tự và số bước di chuyển của mỗi Cube.</t>
+          <t>Xúc xắc sẽ quyết định thứ tự và số bước di chuyển của mỗi Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Việc gieo xúc xắc sẽ quyết định thứ tự và số bước di chuyển của mỗi Cube.</t>
+          <t>Xúc xắc sẽ quyết định thứ tự và số bước di chuyển của mỗi Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Việc gieo xúc xắc sẽ quyết định thứ tự và số bước di chuyển của mỗi Cube.</t>
+          <t>Xúc xắc sẽ quyết định thứ tự và số bước di chuyển của mỗi Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem hướng dẫn chi tiết về Hỗ Trợ Cube.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hướng dẫn chi tiết về Hỗ Trợ Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem hướng dẫn chi tiết về Hỗ Trợ Cube.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hướng dẫn chi tiết về Hỗ Trợ Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem hướng dẫn chi tiết về Hỗ Trợ Cube.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hướng dẫn chi tiết về Hỗ Trợ Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Các Khối Lập Phương đã chuẩn bị xong. Đến lúc chinh phục Abbowser Castle và ngăn chặn Abbowser!</t>
+          <t>Các Khối lập phương đã chuẩn bị xong. Đến lúc chinh phục Lâu đài Abbowser và ngăn chặn Abbowser!</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>{0} Các Khối Lập Phương đã chuẩn bị xong. Đến lúc chinh phục Abbowser Castle và ngăn chặn Abbowser!</t>
+          <t>Đã chuẩn bị xong các Khối Lập Phương rồi {0}. Đến lúc chinh phục Lâu Đài Abbowser và ngăn hắn ta lại!</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Các Khối Lập Phương đã chuẩn bị xong. Đến lúc chinh phục Abbowser Castle và ngăn chặn Abbowser!</t>
+          <t>Các Khối lập phương đã chuẩn bị xong. Đến lúc chinh phục Lâu đài Abbowser và ngăn chặn Abbowser!</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Kiểm tra hiệu ứng lên cấp của Cube tại đây.</t>
+          <t>Xem hiệu ứng lên cấp của Khối Lập Phương tại đây.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Kiểm tra hiệu ứng lên cấp của Cube tại đây.</t>
+          <t>Xem hiệu ứng lên cấp của Khối Lập Phương tại đây.</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Kiểm tra hiệu ứng lên cấp của Cube tại đây.</t>
+          <t>Xem hiệu ứng lên cấp của Khối Lập Phương tại đây.</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để nâng cấp Cube.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để nâng cấp Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để nâng cấp Cube.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để nâng cấp Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để nâng cấp Cube.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để nâng cấp Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Đây là Khả Năng của Cube và chỉ số có thể kích hoạt.</t>
+          <t>Đây là Khả Năng của Khối Lập Phương và các chỉ số có thể kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Đây là Khả Năng của Cube và chỉ số có thể kích hoạt.</t>
+          <t>Đây là Khả Năng của Khối Lập Phương và các chỉ số có thể kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Đây là Khả Năng của Cube và chỉ số có thể kích hoạt.</t>
+          <t>Đây là Khả Năng của Khối Lập Phương và các chỉ số có thể kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hiệu ứng Mô-đun Data tại đây.</t>
+          <t>Cậu có thể xem hiệu ứng của Mô-đun Dữ Liệu ở đây.</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hiệu ứng Mô-đun Data tại đây.</t>
+          <t>Cậu có thể xem hiệu ứng của Mô-đun Dữ Liệu ở đây.</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hiệu ứng Mô-đun Data tại đây.</t>
+          <t>Cậu có thể xem hiệu ứng của Mô-đun Dữ Liệu ở đây.</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để trang bị Data Mô-đun vào ô này.</t>
+          <t>Nhấn để gắn Data Module này vào khe.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để trang bị Data Mô-đun vào ô này.</t>
+          <t>Nhấn để gắn Data Module này vào khe.</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để trang bị Data Mô-đun vào ô này.</t>
+          <t>Nhấn để gắn Data Module này vào khe.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Khu vực phía trước có sự kiện Cốt Truyện Main, nơi diễn ra một phần quan trọng của câu chuyện. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào khu vực để tiếp tục.</t>
+          <t>Khu vực phía trước chứa một sự kiện Cốt Truyện chính, nơi diễn ra phần quan trọng của câu chuyện. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào khu vực để tiếp tục.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Khu vực phía trước có sự kiện Cốt Truyện Main, nơi diễn ra một phần quan trọng của câu chuyện. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào khu vực để tiếp tục.</t>
+          <t>Khu vực phía trước chứa một sự kiện Cốt Truyện chính, nơi diễn ra phần quan trọng của câu chuyện. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào khu vực để tiếp tục.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Khu vực phía trước có sự kiện Cốt Truyện Main, nơi diễn ra một phần quan trọng của câu chuyện. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào khu vực để tiếp tục.</t>
+          <t>Khu vực phía trước chứa một sự kiện Cốt Truyện chính, nơi diễn ra phần quan trọng của câu chuyện. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào khu vực để tiếp tục.</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để phát Film.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để phát Phim.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để phát Film.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để phát Phim.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để phát Film.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để phát Phim.</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Tham gia trận chiến trong Đoạn phim</t>
+          <t>Tham gia trận chiến trong Phim</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Tham gia trận chiến trong Đoạn phim</t>
+          <t>Tham gia trận chiến trong Phim</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Tham gia trận chiến trong Đoạn phim</t>
+          <t>Tham gia trận chiến trong Phim</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Gây DMG sẽ tăng cấp Symphony Rank.</t>
+          <t>Gây Sát Thương sẽ tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Gây DMG sẽ tăng cấp Symphony Rank.</t>
+          <t>Gây Sát Thương sẽ tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Gây DMG sẽ tăng cấp Symphony Rank.</t>
+          <t>Gây Sát Thương sẽ tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Chiêu mộ Resonators tham gia đội của bạn.</t>
+          <t>Mời Resonator gia nhập đội của cậu.</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Chiêu mộ Resonators tham gia đội của bạn.</t>
+          <t>Mời Resonator gia nhập đội của cậu.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Chiêu mộ Resonators tham gia đội của bạn.</t>
+          <t>Mời Resonator gia nhập đội của cậu.</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Các Resonators đã chiêu mộ có thể đồng hành cùng bạn vào thế giới trong Film.</t>
+          <t>Resonator đã chiêu mộ có thể đồng hành cùng cậu vào thế giới của Bộ phim.</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Các Resonators đã chiêu mộ có thể đồng hành cùng bạn vào thế giới trong Film.</t>
+          <t>Resonator đã chiêu mộ có thể đồng hành cùng cậu vào thế giới của Bộ phim.</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Các Resonators đã chiêu mộ có thể đồng hành cùng bạn vào thế giới trong Film.</t>
+          <t>Resonator đã chiêu mộ có thể đồng hành cùng cậu vào thế giới của Bộ phim.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Chiêu mộ Resonators chỉ định để hình thành Bond, mở khóa các hiệu ứng tăng cường mạnh mẽ.</t>
+          <t>Mời Resonator chỉ định để hình thành Mối Liên Kết, mở khóa những hiệu ứng tăng cường mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Chiêu mộ Resonators chỉ định để hình thành Bond, mở khóa các hiệu ứng tăng cường mạnh mẽ.</t>
+          <t>Mời Resonator chỉ định để hình thành Mối Liên Kết, mở khóa những hiệu ứng tăng cường mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Chiêu mộ Resonators chỉ định để hình thành Bond, mở khóa các hiệu ứng tăng cường mạnh mẽ.</t>
+          <t>Mời Resonator chỉ định để hình thành Mối Liên Kết, mở khóa những hiệu ứng tăng cường mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Chọn "Tăng Cường Resonator" để cấp cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
+          <t>Chọn "Resonator Enhancement" để trao cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Chọn "Tăng Cường Resonator" để cấp cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
+          <t>Chọn "Resonator Enhancement" để trao cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Chọn "Tăng Cường Resonator" để cấp cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
+          <t>Chọn "Resonator Enhancement" để trao cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin cơ bản và kỹ năng của Resonator.</t>
+          <t>Bạn có thể xem thông tin cơ bản và kỹ năng của Resonator</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin cơ bản và kỹ năng của Resonator.</t>
+          <t>Bạn có thể xem thông tin cơ bản và kỹ năng của Resonator</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin cơ bản và kỹ năng của Resonator.</t>
+          <t>Bạn có thể xem thông tin cơ bản và kỹ năng của Resonator</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Tuyển dụng hoàn tất. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để thoát Tuyển dụng.</t>
+          <t>Hoàn tất chiêu mộ. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để thoát khỏi giao diện Chiêu mộ.</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>{0} Hoàn tất tuyển dụng. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} để thoát Tuyển dụng.</t>
+          <t>Hoàn tất tuyển dụng. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để thoát Tuyển Dụng.</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tuyển dụng hoàn tất. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để thoát Tuyển dụng.</t>
+          <t>Hoàn tất chiêu mộ. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để thoát khỏi giao diện Chiêu mộ.</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Hoàn thành sự kiện để tăng cấp tất cả Resonators trong đội.</t>
+          <t>Hoàn thành sự kiện để nâng cấp tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Hoàn thành sự kiện để tăng cấp tất cả Resonators trong đội.</t>
+          <t>Hoàn thành sự kiện để nâng cấp tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Hoàn thành sự kiện để tăng cấp tất cả Resonators trong đội.</t>
+          <t>Hoàn thành sự kiện để nâng cấp tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem quy tắc của một bộ phim cụ thể.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc của một bộ Phim cụ thể.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem quy tắc của một bộ phim cụ thể.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc của một bộ Phim cụ thể.</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem quy tắc của một bộ phim cụ thể.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc của một bộ Phim cụ thể.</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Xem buff nhận được sau khi hoàn thành sự kiện tại đây.</t>
+          <t>Xem các hiệu ứng tăng cường nhận được sau khi hoàn thành sự kiện tại đây.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Xem buff nhận được sau khi hoàn thành sự kiện tại đây.</t>
+          <t>Xem các hiệu ứng tăng cường nhận được sau khi hoàn thành sự kiện tại đây.</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Xem buff nhận được sau khi hoàn thành sự kiện tại đây.</t>
+          <t>Xem các hiệu ứng tăng cường nhận được sau khi hoàn thành sự kiện tại đây.</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Concerto Companions được triệu hồi bằng Intro Skill và sẽ tung ra Resonance Liberation khi xuất hiện.</t>
+          <t>Đồng Hành Giao Hưởng được triệu hồi bằng Kỹ Năng Khởi Động và sẽ thi triển Resonance Liberation ngay khi xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Concerto Companions được triệu hồi bằng Intro Skill và sẽ tung ra Resonance Liberation khi xuất hiện.</t>
+          <t>Đồng Hành Giao Hưởng được triệu hồi bằng Kỹ Năng Khởi Động và sẽ thi triển Resonance Liberation ngay khi xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Concerto Companions được triệu hồi bằng Intro Skill và sẽ tung ra Resonance Liberation khi xuất hiện.</t>
+          <t>Đồng Hành Giao Hưởng được triệu hồi bằng Kỹ Năng Khởi Động và sẽ thi triển Resonance Liberation ngay khi xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Bổ sung Concerto Companion vào đội hình để nhận hỗ trợ trong chiến đấu.</t>
+          <t>Thêm một Concerto Companion vào đội hình để nhận được hỗ trợ trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Bổ sung Concerto Companion vào đội hình để nhận hỗ trợ trong chiến đấu.</t>
+          <t>Thêm một Concerto Companion vào đội hình để nhận được hỗ trợ trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Bổ sung Concerto Companion vào đội hình để nhận hỗ trợ trong chiến đấu.</t>
+          <t>Thêm một Concerto Companion vào đội hình để nhận được hỗ trợ trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Tuyển dụng lại cùng một Resonator sẽ tăng Xếp hạng Sao của họ.</t>
+          <t>Chiêu mộ lại cùng một Resonator sẽ tăng Xếp hạng Sao của họ.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Tuyển dụng lại cùng một Resonator sẽ tăng Xếp hạng Sao của họ.</t>
+          <t>Chiêu mộ lại cùng một Resonator sẽ tăng Xếp hạng Sao của họ.</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tuyển dụng lại cùng một Resonator sẽ tăng Xếp hạng Sao của họ.</t>
+          <t>Chiêu mộ lại cùng một Resonator sẽ tăng Xếp hạng Sao của họ.</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Tăng Xếp hạng Sao của Resonator sẽ tăng cường hiệu ứng Liên Kết đặc thù của họ.</t>
+          <t>Tăng Xếp Hạng Sao của Resonator sẽ gia tăng hiệu ứng Liên Kết đặc thù của họ.</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Tăng Xếp hạng Sao của Resonator sẽ tăng cường hiệu ứng Liên Kết đặc thù của họ.</t>
+          <t>Tăng Xếp Hạng Sao của Resonator sẽ gia tăng hiệu ứng Liên Kết đặc thù của họ.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Tăng Xếp hạng Sao của Resonator sẽ tăng cường hiệu ứng Liên Kết đặc thù của họ.</t>
+          <t>Tăng Xếp Hạng Sao của Resonator sẽ gia tăng hiệu ứng Liên Kết đặc thù của họ.</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Bạn có thể tăng Xếp Hạng Sao của Chixia bằng cách chiêu mộ lại cô ấy.</t>
+          <t>Cậu có thể tăng Sao của Chixia bằng cách chiêu mộ lại cô ấy.</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Bạn có thể tăng Xếp Hạng Sao của Chixia bằng cách chiêu mộ lại cô ấy.</t>
+          <t>Cậu có thể tăng Sao của Chixia bằng cách chiêu mộ lại cô ấy.</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Bạn có thể tăng Xếp Hạng Sao của Chixia bằng cách chiêu mộ lại cô ấy.</t>
+          <t>Cậu có thể tăng Sao của Chixia bằng cách chiêu mộ lại cô ấy.</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Sau khi nâng cấp Bond, {Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để xem hiệu ứng của nó.</t>
+          <t>Sau khi nâng cấp Mối Liên Kết, {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sau khi nâng cấp Bond, {Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để xem hiệu ứng của nó.</t>
+          <t>Sau khi nâng cấp Mối Liên Kết, {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Sau khi nâng cấp Bond, {Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để xem hiệu ứng của nó.</t>
+          <t>Sau khi nâng cấp Mối Liên Kết, {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Xem chi tiết Bond và các thành viên tại đây.</t>
+          <t>Xem chi tiết Mối Liên Kết và những ai tham gia tại đây.</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Xem chi tiết Bond và các thành viên tại đây.</t>
+          <t>Xem chi tiết Mối Liên Kết và những ai tham gia tại đây.</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Xem chi tiết Bond và các thành viên tại đây.</t>
+          <t>Xem chi tiết Mối Liên Kết và những ai tham gia tại đây.</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Hiệu ứng Liên Kết của Resonators sẽ kích hoạt khi đạt điều kiện.</t>
+          <t>Hiệu ứng Liên Kết Resonator sẽ kích hoạt khi đạt đủ điều kiện.</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hiệu ứng Liên Kết của Resonators sẽ kích hoạt khi đạt điều kiện.</t>
+          <t>Hiệu ứng Liên Kết Resonator sẽ kích hoạt khi đạt đủ điều kiện.</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hiệu ứng Liên Kết của Resonators sẽ kích hoạt khi đạt điều kiện.</t>
+          <t>Hiệu ứng Liên Kết Resonator sẽ kích hoạt khi đạt đủ điều kiện.</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Khi một Liên Kết được kích hoạt, nó sẽ áp dụng cho toàn đội mà không cần Resonators cụ thể phải có mặt trên chiến trường.</t>
+          <t>Khi một Liên Kết được kích hoạt, nó sẽ áp dụng cho toàn đội mà không cần Resonator cụ thể nào phải có mặt trên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Khi một Liên Kết được kích hoạt, nó sẽ áp dụng cho toàn đội mà không cần Resonators cụ thể phải có mặt trên chiến trường.</t>
+          <t>Khi một Liên Kết được kích hoạt, nó sẽ áp dụng cho toàn đội mà không cần Resonator cụ thể nào phải có mặt trên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Khi một Liên Kết được kích hoạt, nó sẽ áp dụng cho toàn đội mà không cần Resonators cụ thể phải có mặt trên chiến trường.</t>
+          <t>Khi một Liên Kết được kích hoạt, nó sẽ áp dụng cho toàn đội mà không cần Resonator cụ thể nào phải có mặt trên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Kích hoạt Synergy Burst mạnh mẽ trong chiến đấu với 3 Resonators cùng Bond.</t>
+          <t>Kích hoạt Đợt Bùng Nổ Cộng Hưởng mạnh mẽ trong trận chiến với 3 Resonator cùng một Mối Duyên.</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Kích hoạt Synergy Burst mạnh mẽ trong chiến đấu với 3 Resonators cùng Bond.</t>
+          <t>Kích hoạt Đợt Bùng Nổ Cộng Hưởng mạnh mẽ trong trận chiến với 3 Resonator cùng một Mối Duyên.</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Kích hoạt Synergy Burst mạnh mẽ trong chiến đấu với 3 Resonators cùng Bond.</t>
+          <t>Kích hoạt Đợt Bùng Nổ Cộng Hưởng mạnh mẽ trong trận chiến với 3 Resonator cùng một Mối Duyên.</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Synergy Burst có thể được thi triển chủ động trong trận chiến để cung cấp nhiều buff.</t>
+          <t>Cộng Hưởng Bùng Nổ có thể kích hoạt chủ động trong trận chiến để mang lại nhiều hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Synergy Burst có thể được thi triển chủ động trong trận chiến để cung cấp nhiều buff.</t>
+          <t>Cộng Hưởng Bùng Nổ có thể kích hoạt chủ động trong trận chiến để mang lại nhiều hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Synergy Burst có thể được thi triển chủ động trong trận chiến để cung cấp nhiều buff.</t>
+          <t>Cộng Hưởng Bùng Nổ có thể kích hoạt chủ động trong trận chiến để mang lại nhiều hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Một đội hình gồm Resonators cụ thể sẽ mở khóa hiệu ứng Synergy Burst đặc biệt.</t>
+          <t>Một đội hình Resonator cụ thể sẽ mở khóa hiệu ứng Đồng Bộ Bùng Nổ đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Một đội hình gồm Resonators cụ thể sẽ mở khóa hiệu ứng Synergy Burst đặc biệt.</t>
+          <t>Một đội hình Resonator cụ thể sẽ mở khóa hiệu ứng Đồng Bộ Bùng Nổ đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Một đội hình gồm Resonators cụ thể sẽ mở khóa hiệu ứng Synergy Burst đặc biệt.</t>
+          <t>Một đội hình Resonator cụ thể sẽ mở khóa hiệu ứng Đồng Bộ Bùng Nổ đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Bao gồm Jiyan, Chixia và Rover trong đội hình để mở khóa hiệu ứng Synergy Burst đặc biệt!</t>
+          <t>Bổ sung Jiyan, Chixia và Rover vào đội hình để mở khóa hiệu ứng Đồng Điệu Bùng Nổ đặc biệt!</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Bao gồm Jiyan, Chixia và Rover trong đội hình để mở khóa hiệu ứng Synergy Burst đặc biệt!</t>
+          <t>Bổ sung Jiyan, Chixia và Rover vào đội hình để mở khóa hiệu ứng Đồng Điệu Bùng Nổ đặc biệt!</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Bao gồm Jiyan, Chixia và Rover trong đội hình để mở khóa hiệu ứng Synergy Burst đặc biệt!</t>
+          <t>Bổ sung Jiyan, Chixia và Rover vào đội hình để mở khóa hiệu ứng Đồng Điệu Bùng Nổ đặc biệt!</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} vào đây để xem quy tắc Film Roll.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc của Cuộn Phim.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} vào đây để xem quy tắc Film Roll.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc của Cuộn Phim.</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} vào đây để xem quy tắc Film Roll.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc của Cuộn Phim.</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Gây DMG và Dodge thành công sẽ tăng Synergy.</t>
+          <t>Gây Sát Thương và Né Tránh thành công sẽ tăng Độ Đồng Bộ.</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Gây DMG và Dodge thành công sẽ tăng Synergy.</t>
+          <t>Gây Sát Thương và Né Tránh thành công sẽ tăng Độ Đồng Bộ.</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Gây DMG và Dodge thành công sẽ tăng Synergy.</t>
+          <t>Gây Sát Thương và Né Tránh thành công sẽ tăng Độ Đồng Bộ.</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để giải phóng Synergy Burst.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để giải phóng Đồng Điệu Bùng Nổ.</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=press Gamepad=press} để giải phóng Synergy Burst</t>
+          <t>Nhấn {0} {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để giải phóng Cơn Bùng Nổ Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để giải phóng Synergy Burst.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để giải phóng Đồng Điệu Bùng Nổ.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Token cung cấp hiệu ứng buff mạnh mẽ.</t>
+          <t>Mã thông báo mang lại hiệu ứng tăng cường mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Token cung cấp hiệu ứng buff mạnh mẽ.</t>
+          <t>Mã thông báo mang lại hiệu ứng tăng cường mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Token cung cấp hiệu ứng buff mạnh mẽ.</t>
+          <t>Mã thông báo mang lại hiệu ứng tăng cường mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để kiểm tra nhanh hiệu ứng Liên Kết của bạn.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để kiểm tra nhanh hiệu ứng Liên Kết.</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để nhanh chóng kiểm tra hiệu ứng Bond</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để kiểm tra nhanh hiệu ứng Liên Kết.</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để kiểm tra nhanh hiệu ứng Liên Kết của bạn.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để kiểm tra nhanh hiệu ứng Liên Kết.</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem chi tiết hiệu ứng Cấp Đội.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết hiệu ứng Cấp Đội.</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem chi tiết hiệu ứng Cấp Đội.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết hiệu ứng Cấp Đội.</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem chi tiết hiệu ứng Cấp Đội.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết hiệu ứng Cấp Đội.</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem quy tắc Cấp Đội.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc về Cấp Độ Đội.</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem quy tắc Cấp Đội.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc về Cấp Độ Đội.</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem quy tắc Cấp Đội.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem quy tắc về Cấp Độ Đội.</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>&lt;texture=/Game/Aki/UI/UIResources/Common/Image/UiIconPcBtn/T_IconPcBtn_KeyAlt_UI.T_IconPcBtn_KeyAlt_UI/&gt;+&lt;texture=/Game/Aki/UI/UIResources/Common/Image/UiIconPcBtn/T_IconPcBtn_KeyC_UI.T_IconPcBtn_KeyC_UI/&gt; để nhanh chóng &lt;color=#8c7e51&gt;vào&lt;/color&gt; hoặc &lt;color=#8c7e51&gt;thoát&lt;/color&gt; Chế Độ Hòa Nhập.</t>
+          <t>Nhấn &lt;texture=/Game/Aki/UI/UIResources/Common/Image/UiIconPcBtn/T_IconPcBtn_KeyAlt_UI.T_IconPcBtn_KeyAlt_UI/&gt;+&lt;texture=/Game/Aki/UI/UIResources/Common/Image/UiIconPcBtn/T_IconPcBtn_KeyC_UI.T_IconPcBtn_KeyC_UI/&gt; để nhanh chóng &lt;color=#8c7e51&gt;nhập&lt;/color&gt; hoặc &lt;color=#8c7e51&gt;thoát&lt;/color&gt; Chế Độ Hòa Nhập.</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>{0} + {1} để nhanh chóng &lt;color=#8c7e51&gt;vào&lt;/color&gt; hoặc &lt;color=#8c7e51&gt;thoát&lt;/color&gt; Chế độ Immersion.</t>
+          <t>{0} + {1} để nhanh chóng &lt;color=#8c7e51&gt;đi vào&lt;/color&gt; hoặc &lt;color=#8c7e51&gt;thoát khỏi&lt;/color&gt; Chế Độ Hòa Nhập.</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để thoát Chế Độ Hòa Nhập.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để thoát Chế Độ Hòa Nhập.</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Đổi Protagonist và đặt Chixia làm Protagonist.</t>
+          <t>Đổi Resonator chính và đặt Chixia làm nhân vật chính.</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Đổi Protagonist và đặt Chixia làm Protagonist.</t>
+          <t>Đổi Resonator chính và đặt Chixia làm nhân vật chính.</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Đổi Protagonist và đặt Chixia làm Protagonist.</t>
+          <t>Đổi Resonator chính và đặt Chixia làm nhân vật chính.</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để Chixia xuất hiện trong Film.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để Chixia xuất hiện trong Phim.</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để Chixia xuất hiện trong Film.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để Chixia xuất hiện trong Phim.</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để Chixia xuất hiện trong Film.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để Chixia xuất hiện trong Phim.</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Đặt Chixia làm Main Resonator.</t>
+          <t>Chọn Chixia làm Resonator Chính.</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Đặt Chixia làm Main Resonator.</t>
+          <t>Chọn Chixia làm Resonator Chính.</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Đặt Chixia làm Main Resonator.</t>
+          <t>Chọn Chixia làm Resonator Chính.</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Tính Năng Fast Track</t>
+          <t>Tính năng Theo Dấu Nhanh</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Tính Năng Fast Track</t>
+          <t>Tính năng Theo Dấu Nhanh</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Tính Năng Fast Track</t>
+          <t>Tính năng Theo Dấu Nhanh</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi Thuộc Tính Resonance của Rover tại đây.</t>
+          <t>Bạn có thể thay đổi Thuộc Tính Cộng Hưởng của Rover tại đây.</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi Thuộc Tính Resonance của Rover tại đây.</t>
+          <t>Bạn có thể thay đổi Thuộc Tính Cộng Hưởng của Rover tại đây.</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi Thuộc Tính Resonance của Rover tại đây.</t>
+          <t>Bạn có thể thay đổi Thuộc Tính Cộng Hưởng của Rover tại đây.</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Duelist, chào mừng đến với Peaks of Prestige! Tôi sẽ hướng dẫn bạn các quy tắc cơ bản của trò chơi.</t>
+          <t>Duelist, chào mừng đến với Đỉnh Vinh Quang! Ta sẽ hướng dẫn ngươi những luật cơ bản của trò chơi này.</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Duelist, chào mừng đến với Peaks of Prestige! Tôi sẽ hướng dẫn bạn các quy tắc cơ bản của trò chơi.</t>
+          <t>Duelist, chào mừng đến với Đỉnh Vinh Quang! Ta sẽ hướng dẫn ngươi những luật cơ bản của trò chơi này.</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Duelist, chào mừng đến với Peaks of Prestige! Tôi sẽ hướng dẫn bạn các quy tắc cơ bản của trò chơi.</t>
+          <t>Duelist, chào mừng đến với Đỉnh Vinh Quang! Ta sẽ hướng dẫn ngươi những luật cơ bản của trò chơi này.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Trong Đỉnh Cao Uy Danh, mục tiêu là nâng cấp Echoes và củng cố đội hình để đánh bại đối thủ.</t>
+          <t>Tại Đỉnh Vinh Quang, mục tiêu là nâng cấp Echo và củng cố đội hình để đánh bại đối thủ.</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Trong Đỉnh Cao Uy Danh, mục tiêu là nâng cấp Echoes và củng cố đội hình để đánh bại đối thủ.</t>
+          <t>Tại Đỉnh Vinh Quang, mục tiêu là nâng cấp Echo và củng cố đội hình để đánh bại đối thủ.</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Trong Đỉnh Cao Uy Danh, mục tiêu là nâng cấp Echoes và củng cố đội hình để đánh bại đối thủ</t>
+          <t>Tại Đỉnh Vinh Quang, mục tiêu là nâng cấp Echo và củng cố đội hình để đánh bại đối thủ.</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Đối thủ luôn đi trước trong Đỉnh Danh Vọng.</t>
+          <t>Trong Peaks of Prestige, đối thủ của cậu luôn đi trước.</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Đối thủ luôn đi trước trong Đỉnh Danh Vọng.</t>
+          <t>Trong Peaks of Prestige, đối thủ của cậu luôn đi trước.</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Đối thủ luôn đi trước trong Đỉnh Danh Vọng.</t>
+          <t>Trong Peaks of Prestige, đối thủ của cậu luôn đi trước.</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Bạn đã hết Energy. Nhưng bạn có thể &lt;color=#8c7e51&gt;Reconstruct&lt;/color&gt; các Echoes không cần thiết để nhận thêm Energy.</t>
+          <t>Năng lượng của cậu đã cạn kiệt. Nhưng cậu có thể &lt;color=#8c7e51&gt;Tái Cấu Trúc&lt;/color&gt; những Echo không cần thiết để lấy thêm Năng lượng.</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Bạn đã hết Energy. Nhưng bạn có thể &lt;color=#8c7e51&gt;Reconstruct&lt;/color&gt; các Echoes không cần thiết để nhận thêm Energy.</t>
+          <t>Năng lượng của cậu đã cạn kiệt. Nhưng cậu có thể &lt;color=#8c7e51&gt;Tái Cấu Trúc&lt;/color&gt; những Echo không cần thiết để lấy thêm Năng lượng.</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Bạn đã hết Energy. Nhưng bạn có thể &lt;color=#8c7e51&gt;Reconstruct&lt;/color&gt; các Echoes không cần thiết để nhận thêm Energy.</t>
+          <t>Năng lượng của cậu đã cạn kiệt. Nhưng cậu có thể &lt;color=#8c7e51&gt;Tái Cấu Trúc&lt;/color&gt; những Echo không cần thiết để lấy thêm Năng lượng.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Đây là Khu Tái Thiết. Place một Echo tại đây để &lt;color=#8c7e51&gt;nhận 1 điểm Năng Lượng&lt;/color&gt;.</t>
+          <t>Đây là Khu Tái Tạo. Đặt một Echo vào đây để &lt;color=#8c7e51&gt;nhận 1 điểm Năng Lượng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Đây là Khu Tái Thiết. Place một Echo tại đây để &lt;color=#8c7e51&gt;nhận 1 điểm Năng Lượng&lt;/color&gt;.</t>
+          <t>Đây là Khu Tái Tạo. Đặt một Echo vào đây để &lt;color=#8c7e51&gt;nhận 1 điểm Năng Lượng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Đây là Khu Tái Thiết. Place một Echo tại đây để &lt;color=#8c7e51&gt;nhận 1 điểm Năng Lượng&lt;/color&gt;.</t>
+          <t>Đây là Khu Tái Tạo. Đặt một Echo vào đây để &lt;color=#8c7e51&gt;nhận 1 điểm Năng Lượng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Thử kéo một lá bài trên tay vào Khu Tái Thiết.</t>
+          <t>Thử kéo một lá bài trên tay vào Khu Vực Tái Cấu Trúc xem.</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Chọn một thẻ trên tay và giữ {0} để Tái Cấu Trúc.</t>
+          <t>Chọn một lá bài trên tay và giữ {0} để Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Thử kéo một lá bài trên tay vào Khu Tái Thiết.</t>
+          <t>Thử kéo một lá bài trên tay vào Khu Vực Tái Cấu Trúc xem.</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Xem mẹo và chiến thuật trong bách khoa thư Peaks of Prestige tại đây.</t>
+          <t>Xem mẹo và chiến thuật trong bộ bách khoa Peaks of Prestige tại đây.</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>{0} Xem mẹo và chiến thuật trong bách khoa thư Peaks of Prestige tại đây.</t>
+          <t>Xem mẹo và chiến thuật trong bách khoa thư Peaks of Prestige tại đây.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Xem mẹo và chiến thuật trong bách khoa thư Peaks of Prestige tại đây.</t>
+          <t>Xem mẹo và chiến thuật trong bộ bách khoa Peaks of Prestige tại đây.</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Tiêu hao Energy để sử dụng Resonator Tactics và nhận buff trong trận đấu.</t>
+          <t>Tiêu hao Năng Lượng để sử dụng Chiến Thuật Resonator và nhận hiệu ứng tăng cường trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Tiêu hao Energy để sử dụng Resonator Tactics và nhận buff trong trận đấu.</t>
+          <t>Tiêu hao Năng Lượng để sử dụng Chiến Thuật Resonator và nhận hiệu ứng tăng cường trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Tiêu hao Energy để sử dụng Resonator Tactics và nhận buff trong trận đấu.</t>
+          <t>Tiêu hao Năng Lượng để sử dụng Chiến Thuật Resonator và nhận hiệu ứng tăng cường trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Core Echoes cực kỳ mạnh mẽ, nhưng bạn cần hoàn thành Trial tương ứng để thêm một cái vào bộ bài của mình.</t>
+          <t>Tâm Ảnh Cốt Lõi cực kỳ mạnh mẽ, nhưng cậu cần hoàn thành Thử Thách tương ứng để thêm vào bộ bài của mình.</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Core Echoes cực kỳ mạnh mẽ, nhưng bạn cần hoàn thành Trial tương ứng để thêm một cái vào bộ bài của mình.</t>
+          <t>Tâm Ảnh Cốt Lõi cực kỳ mạnh mẽ, nhưng cậu cần hoàn thành Thử Thách tương ứng để thêm vào bộ bài của mình.</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Core Echoes cực kỳ mạnh mẽ, nhưng bạn cần hoàn thành Trial tương ứng để thêm một cái vào bộ bài của mình.</t>
+          <t>Tâm Ảnh Cốt Lõi cực kỳ mạnh mẽ, nhưng cậu cần hoàn thành Thử Thách tương ứng để thêm vào bộ bài của mình.</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} để xem Echo Cốt lõi và Trial.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Echo Cốt Lõi và Thử Nghiệm.</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem Core Echo và Thử Nghiệm.</t>
+          <t>Nhấn {0} để xem Core Echo và Thử Nghiệm</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} để xem Echo Cốt lõi và Trial.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Echo Cốt Lõi và Thử Nghiệm.</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tốc độ chiến đấu có thể điều chỉnh tại đây.</t>
+          <t>Tốc độ trận chiến có thể điều chỉnh tại đây.</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Tốc độ chiến đấu có thể điều chỉnh tại đây.</t>
+          <t>Tốc độ trận chiến có thể điều chỉnh tại đây.</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Tốc độ chiến đấu có thể điều chỉnh tại đây.</t>
+          <t>Tốc độ trận chiến có thể điều chỉnh tại đây.</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Chọn một Trial Khủng Hoảng tại đây để bắt đầu.</t>
+          <t>Chọn Thử Thách Khủng Hoảng tại đây để bắt đầu</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Chọn một Trial Khủng Hoảng tại đây để bắt đầu.</t>
+          <t>Chọn Thử Thách Khủng Hoảng tại đây để bắt đầu</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chọn một Trial Khủng Hoảng tại đây để bắt đầu.</t>
+          <t>Chọn Thử Thách Khủng Hoảng tại đây để bắt đầu</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Cấp Độ Duelist của bạn đã tăng. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem phần thưởng theo cấp.</t>
+          <t>Cấp độ Kẻ Đấu của cậu đã được nâng lên. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem phần thưởng cấp độ.</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Cấp Độ Duelist của bạn đã tăng. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem phần thưởng theo cấp.</t>
+          <t>Cấp độ Kẻ Đấu của cậu đã được nâng lên. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem phần thưởng cấp độ.</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Cấp Độ Duelist của bạn đã tăng. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem phần thưởng theo cấp.</t>
+          <t>Cấp độ Kẻ Đấu của cậu đã được nâng lên. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem phần thưởng cấp độ.</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để di chuyển nhanh đến gần "Lãnh Chúa Prestige" tiếp theo.</t>
+          <t>Nhấn vào đây để dịch chuyển tức thời đến gần "Lãnh Chúa Uy Tín" tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để di chuyển nhanh đến gần "Lãnh Chúa Prestige" tiếp theo.</t>
+          <t>Nhấn vào đây để dịch chuyển tức thời đến gần "Lãnh Chúa Uy Tín" tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để di chuyển nhanh đến gần "Lãnh Chúa Prestige" tiếp theo.</t>
+          <t>Nhấn vào đây để dịch chuyển tức thời đến gần "Lãnh Chúa Uy Tín" tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Chức năng xây dựng Bộ Hồi đã mở khóa. Bạn có thể chỉnh sửa bộ hồi tại đây.</t>
+          <t>Đã mở khóa tạo bộ bài. Bạn có thể chỉnh sửa bộ bài tại đây.</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>{0} Xây dựng Bộ Echo đã khả dụng. Bạn có thể chỉnh sửa bộ Echo của mình tại đây.</t>
+          <t>Chức năng xây dựng bộ bài đã mở. Bạn có thể chỉnh sửa bộ bài tại đây.</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Chức năng xây dựng Bộ Hồi đã mở khóa. Bạn có thể chỉnh sửa bộ hồi tại đây.</t>
+          <t>Đã mở khóa tạo bộ bài. Bạn có thể chỉnh sửa bộ bài tại đây.</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để thêm bộ bài. Bạn có thể tùy chỉnh bộ bài để đối phó với các đối thủ khác nhau.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để thêm bộ bài. Bạn có thể tùy chỉnh bộ bài cho từng đối thủ khác nhau.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để thêm bộ bài. Bạn có thể tùy chỉnh bộ bài để đối phó với các đối thủ khác nhau.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để thêm bộ bài. Bạn có thể tùy chỉnh bộ bài cho từng đối thủ khác nhau.</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để thêm bộ bài. Bạn có thể tùy chỉnh bộ bài để đối phó với các đối thủ khác nhau.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để thêm bộ bài. Bạn có thể tùy chỉnh bộ bài cho từng đối thủ khác nhau.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào Echo để thêm vào bộ bài.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào Echo để thêm vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào Echo để thêm vào bộ bài.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào Echo để thêm vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} một Echo để thêm vào bộ bài.</t>
+          <t>Nhấn vào Echo để thêm nó vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Bạn cần có số lượng Echoes tối thiểu trong bộ bài để đấu.</t>
+          <t>Bạn cần có số lượng Tacet Discord tối thiểu trong bộ bài để tham gia trận đấu.</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>{0} Bạn cần tối thiểu số lượng Echoes trong bộ bài để đấu.</t>
+          <t>{0} Cậu cần có số lượng Echo tối thiểu trong bộ bài để tham gia đấu.</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Bạn cần có số lượng Echoes tối thiểu trong bộ bài để đấu.</t>
+          <t>Bạn cần có số lượng Tacet Discord tối thiểu trong bộ bài để tham gia trận đấu.</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=Chọn} một Echo để loại khỏi bộ bài. Giữ một Echo trong danh sách để xem chi tiết.</t>
+          <t>Chọn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Select} một Echo để loại khỏi bộ bài. Giữ Echo trong danh sách để xem chi tiết.</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=Touch PC=click Gamepad=Chọn} một Echo để gỡ khỏi bộ bài. Giữ một Echo trong danh sách để xem chi tiết.</t>
+          <t>Chọn {0} một Echo để loại khỏi bộ bài. Giữ Echo trong danh sách để xem chi tiết</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=Chọn} một Echo để loại khỏi bộ bài. Giữ một Echo trong danh sách để xem chi tiết.</t>
+          <t>Chọn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Select} một Echo để loại khỏi bộ bài. Giữ Echo trong danh sách để xem chi tiết.</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Sử dụng chức năng Xây dựng Nhanh để thiết lập bộ bài theo cài đặt sẵn.</t>
+          <t>Dùng chức năng Xây Dựng Nhanh để thiết lập bộ bài theo cài đặt sẵn.</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Giữ {0} để dùng chức năng Build Nhanh và thiết lập bộ bài theo thiết lập có sẵn.</t>
+          <t>Giữ để sử dụng chức năng Xây Dựng Nhanh và thiết lập bộ bài theo cài đặt sẵn.</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Sử dụng chức năng Xây dựng Nhanh để thiết lập bộ bài theo cài đặt sẵn.</t>
+          <t>Dùng chức năng Xây Dựng Nhanh để thiết lập bộ bài theo cài đặt sẵn.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Bạn đã sở hữu tất cả Echoes trong bộ cài đặt này.</t>
+          <t>Bạn đã sở hữu tất cả Echo trong bộ bài dựng sẵn này.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Bạn đã sở hữu tất cả Echoes trong bộ cài đặt này.</t>
+          <t>Bạn đã sở hữu tất cả Echo trong bộ bài dựng sẵn này.</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Bạn đã sở hữu tất cả Echoes trong bộ cài đặt này.</t>
+          <t>Bạn đã sở hữu tất cả Echo trong bộ bài dựng sẵn này.</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xây dựng bộ bài ngay theo cài đặt sẵn.</t>
+          <t>Nhấn vào đây để xây dựng bộ bài của bạn ngay lập tức theo thiết lập có sẵn.</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xây dựng bộ bài ngay theo cài đặt sẵn.</t>
+          <t>Nhấn vào đây để xây dựng bộ bài của bạn ngay lập tức theo thiết lập có sẵn.</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xây dựng bộ bài ngay theo cài đặt sẵn.</t>
+          <t>Nhấn vào đây để xây dựng bộ bài của bạn ngay lập tức theo thiết lập có sẵn.</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem hướng dẫn chỉnh sửa bộ bài.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem hướng dẫn chỉnh sửa bộ bài.</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>{0} View hướng dẫn chỉnh sửa bộ bài.</t>
+          <t>Xem hướng dẫn chỉnh sửa bộ bài.</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem hướng dẫn chỉnh sửa bộ bài.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem hướng dẫn chỉnh sửa bộ bài.</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem thông tin đối thủ và trận đấu này.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem thông tin về đối thủ và trận đấu này.</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem thông tin đối thủ và trận đấu này.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem thông tin về đối thủ và trận đấu này.</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem thông tin đối thủ và trận đấu này.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem thông tin về đối thủ và trận đấu này.</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Bạn phải chọn Resonator Tactics và bộ bài trước khi đấu.</t>
+          <t>Cậu phải chọn Chiến Thuật Resonator và bộ bài trước khi đấu.</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Bạn phải chọn Resonator Tactics và bộ bài trước khi đấu.</t>
+          <t>Cậu phải chọn Chiến Thuật Resonator và bộ bài trước khi đấu.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Bạn phải chọn Resonator Tactics và bộ bài trước khi đấu.</t>
+          <t>Cậu phải chọn Chiến Thuật Resonator và bộ bài trước khi đấu.</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>{0} Bộ bài phải bao gồm một Core Echo.</t>
+          <t>{0} Bộ bài phải bao gồm một Tổ Tacet Cốt Lõi.</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Add Core Echo vào bộ bài của bạn.</t>
+          <t>Thêm Tâm Ảnh Hạch vào bộ bài của bạn.</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>{0} Add Echo Cốt Core vào bộ bài của bạn.</t>
+          <t>{0} Thêm Tổ Tacet Cốt Lõi vào bộ bài của bạn.</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Add Core Echo vào bộ bài của bạn.</t>
+          <t>Thêm Tâm Ảnh Hạch vào bộ bài của bạn.</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem hoặc mở khóa Echoes bạn chưa sở hữu.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hoặc mở khóa các Echo bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem hoặc mở khóa Echoes bạn chưa sở hữu.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hoặc mở khóa các Echo bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem hoặc mở khóa Echoes bạn chưa sở hữu.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hoặc mở khóa các Echo bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem thông tin các lá bài bạn chưa sở hữu.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem thông tin về các thẻ bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>{0} View thông tin các thẻ bạn chưa sở hữu.</t>
+          <t>Xem thông tin về những lá bài ngươi chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem thông tin các lá bài bạn chưa sở hữu.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem thông tin về các thẻ bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Prestige Points có thể dùng để mở khóa các Echoes bạn chưa sở hữu.</t>
+          <t>Điểm Uy Tín có thể dùng để mở khóa Echo mà bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Prestige Points có thể dùng để mở khóa các Echoes bạn chưa sở hữu.</t>
+          <t>Điểm Uy Tín có thể dùng để mở khóa Echo mà bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Prestige Points có thể dùng để mở khóa các Echoes bạn chưa sở hữu.</t>
+          <t>Điểm Uy Tín có thể dùng để mở khóa Echo mà bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Trong chế độ Endless Challenge, bạn có thể đối đầu với đối thủ có bộ bài thuộc Nguyên Tố ngẫu nhiên.</t>
+          <t>Trong Chế Độ Thử Thách Vô Tận, ngươi có thể đối đầu với những đối thủ sở hữu bộ bài ngẫu nhiên thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Trong chế độ Endless Challenge, bạn có thể đối đầu với đối thủ có bộ bài thuộc Nguyên Tố ngẫu nhiên.</t>
+          <t>Trong Chế Độ Thử Thách Vô Tận, ngươi có thể đối đầu với những đối thủ sở hữu bộ bài ngẫu nhiên thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Trong chế độ Endless Challenge, bạn có thể đối đầu với đối thủ có bộ bài thuộc Nguyên Tố ngẫu nhiên.</t>
+          <t>Trong Chế Độ Thử Thách Vô Tận, ngươi có thể đối đầu với những đối thủ sở hữu bộ bài ngẫu nhiên thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Sự kiện "Banners Never Fall" đã bắt đầu. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Chi Tiết Khu Vực Challenge và phần thưởng.</t>
+          <t>Sự kiện "Ngọn Cờ Bất Diệt" đã chính thức bắt đầu. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để kiểm tra Khu Vực Thách Đấu và xem chi tiết phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>{0}+{1} Sự kiện "Banners Never Fall" đã bắt đầu. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem khu vực thử thách và thông tin phần thưởng.</t>
+          <t>{0}+{1} Sự kiện "Lá Cờ Không Bại" đã bắt đầu. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem khu vực thử thách và thông tin phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Sự kiện "Banners Never Fall" đã bắt đầu. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem thông tin về khu vực thử thách và phần thưởng.</t>
+          <t>Sự kiện "Ngọn Cờ Bất Diệt" đã bắt đầu. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem thông tin về khu vực thách đấu và phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem thông tin khu vực.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem thông tin khu vực.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem thông tin khu vực.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem thông tin khu vực.</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem thông tin khu vực.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem thông tin khu vực.</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thu thập Rương Chiến Công trong Khu Vực Challenge.</t>
+          <t>Màn hình này hiển thị tiến độ thu thập Rương Chiến Lợi Phẩm trong Khu Vực Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thu thập Rương Chiến Công trong Khu Vực Challenge.</t>
+          <t>Màn hình này hiển thị tiến độ thu thập Rương Chiến Lợi Phẩm trong Khu Vực Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thu thập Rương Chiến Công trong Khu Vực Challenge.</t>
+          <t>Màn hình này hiển thị tiến độ thu thập Rương Chiến Lợi Phẩm trong Khu Vực Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Mỗi khu vực chứa nhiều mục tiêu thử thách để lựa chọn.</t>
+          <t>Mỗi khu vực có nhiều mục tiêu thử thách để lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Mỗi khu vực chứa nhiều mục tiêu thử thách để lựa chọn.</t>
+          <t>Mỗi khu vực có nhiều mục tiêu thử thách để lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Mỗi khu vực chứa nhiều mục tiêu thử thách để lựa chọn.</t>
+          <t>Mỗi khu vực có nhiều mục tiêu thử thách để lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Đánh bại Zone Elite sẽ chiếm lĩnh toàn bộ khu vực, hoặc bạn có thể hoàn thành từng thử thách một.</t>
+          <t>Đánh bại Tinh Anh Khu Vực sẽ chiếm lĩnh toàn bộ khu vực, hoặc bạn có thể chinh phục từng thử thách một.</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Đánh bại Zone Elite sẽ chiếm lĩnh toàn bộ khu vực, hoặc bạn có thể hoàn thành từng thử thách một.</t>
+          <t>Đánh bại Tinh Anh Khu Vực sẽ chiếm lĩnh toàn bộ khu vực, hoặc bạn có thể chinh phục từng thử thách một.</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Đánh bại Zone Elite sẽ chiếm lĩnh toàn bộ khu vực, hoặc bạn có thể hoàn thành từng thử thách một.</t>
+          <t>Đánh bại Tinh Anh Khu Vực sẽ chiếm lĩnh toàn bộ khu vực, hoặc bạn có thể chinh phục từng thử thách một.</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Elite trong khu vực, Rương Báu Ẩn trong khu vực sẽ hiện trên bản đồ.</t>
+          <t>Sau khi đánh bại Kẻ Địch Đặc Biệt trong khu vực, các Rương Chiến Lợi Phẩm ẩn sẽ hiện ra trên bản đồ.</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Elite trong khu vực, Rương Báu Ẩn trong khu vực sẽ hiện trên bản đồ.</t>
+          <t>Sau khi đánh bại Kẻ Địch Đặc Biệt trong khu vực, các Rương Chiến Lợi Phẩm ẩn sẽ hiện ra trên bản đồ.</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Elite trong khu vực, Rương Báu Ẩn trong khu vực sẽ hiện trên bản đồ.</t>
+          <t>Sau khi đánh bại Kẻ Địch Đặc Biệt trong khu vực, các Rương Chiến Lợi Phẩm ẩn sẽ hiện ra trên bản đồ.</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Xem các buff đang hoạt động trong thử thách tại đây.</t>
+          <t>Xem các hiệu ứng tăng cường đang hoạt động trong thử thách tại đây.</t>
         </is>
       </c>
     </row>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>{0} View các buff đang hoạt động trong thử thách tại đây.</t>
+          <t>Xem các hiệu ứng tăng cường đang hoạt động trong thử thách tại đây.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Xem các buff đang hoạt động trong thử thách tại đây.</t>
+          <t>Xem các hiệu ứng tăng cường đang hoạt động trong thử thách tại đây.</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Khám phá khu vực sẽ tăng Cấp Glory và nâng cao chỉ số Resonator của bạn.</t>
+          <t>Khám phá khu vực sẽ tăng Cấp Vinh Quang và nâng cao chỉ số Resonator của bạn.</t>
         </is>
       </c>
     </row>
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Khám phá khu vực sẽ tăng Cấp Glory và nâng cao chỉ số Resonator của bạn.</t>
+          <t>Khám phá khu vực sẽ tăng Cấp Vinh Quang và nâng cao chỉ số Resonator của bạn.</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Khám phá khu vực sẽ tăng Cấp Glory và nâng cao chỉ số Resonator của bạn.</t>
+          <t>Khám phá khu vực sẽ tăng Cấp Vinh Quang và nâng cao chỉ số Resonator của bạn.</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Tấn công kẻ địch sẽ nhận Battle Engagement Points để tăng sức mạnh chiến đấu.</t>
+          <t>Tấn Công kẻ địch sẽ tích lũy Điểm Tham Chiến, tăng sức mạnh chiến đấu của cậu.</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Tấn công kẻ địch sẽ nhận Battle Engagement Points để tăng sức mạnh chiến đấu.</t>
+          <t>Tấn Công kẻ địch sẽ tích lũy Điểm Tham Chiến, tăng sức mạnh chiến đấu của cậu.</t>
         </is>
       </c>
     </row>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Tấn công kẻ địch sẽ nhận Battle Engagement Points để tăng sức mạnh chiến đấu.</t>
+          <t>Tấn Công kẻ địch sẽ tích lũy Điểm Tham Chiến, tăng sức mạnh chiến đấu của cậu.</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Đối thủ đã Triển Khai xong. Bạn có thể xem Triển Khai của họ ngay bây giờ.</t>
+          <t>Đối thủ đã triển khai xong. Giờ cậu có thể xem Đội Hình của họ.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Đối thủ đã Triển Khai xong. Bạn có thể xem Triển Khai của họ ngay bây giờ.</t>
+          <t>Đối thủ đã triển khai xong. Giờ cậu có thể xem Đội Hình của họ.</t>
         </is>
       </c>
     </row>
